--- a/BTS SIO - 2025 - Epreuve E5 - Tableau de synthèse.xlsx
+++ b/BTS SIO - 2025 - Epreuve E5 - Tableau de synthèse.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grego\Documents\Epsi\B1\Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grego\Documents\Epsi\B1\Portfolio\Portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D137A6CA-53BF-4994-BD72-0A4E2FCFD756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9353D40B-982F-4BEA-A305-3AD1E3112174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -187,7 +187,7 @@
     <t>Centre de formation : EPSI Montpellier</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio : mylow04.github.io/</t>
+    <t>Adresse URL du portfolio : mylow04.github.io/Portfolio</t>
   </si>
 </sst>
 </file>
@@ -2271,17 +2271,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="40db4c2f-5dfe-4423-b7fa-968caa59f9fe" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="94eab51b-fcae-4bce-a35e-bdc099b66db8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D13F0084B24AA74087E0D5FB9F267B1F" ma:contentTypeVersion="15" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="31229381912a9b69d764de2096ccdf03">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40db4c2f-5dfe-4423-b7fa-968caa59f9fe" xmlns:ns3="94eab51b-fcae-4bce-a35e-bdc099b66db8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4f9c18c7f25620f8c3cb0c17c1355e34" ns2:_="" ns3:_="">
     <xsd:import namespace="40db4c2f-5dfe-4423-b7fa-968caa59f9fe"/>
@@ -2516,6 +2505,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="40db4c2f-5dfe-4423-b7fa-968caa59f9fe" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="94eab51b-fcae-4bce-a35e-bdc099b66db8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB576EC0-5DC1-406F-8CC8-5E3BD2560CB9}">
   <ds:schemaRefs>
@@ -2525,17 +2525,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FD341B9-B5DF-4F14-965D-9EDA5A4C842B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="40db4c2f-5dfe-4423-b7fa-968caa59f9fe"/>
-    <ds:schemaRef ds:uri="94eab51b-fcae-4bce-a35e-bdc099b66db8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{362E6B38-63C3-46CF-B34D-64B772DABA7B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2552,4 +2541,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FD341B9-B5DF-4F14-965D-9EDA5A4C842B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="40db4c2f-5dfe-4423-b7fa-968caa59f9fe"/>
+    <ds:schemaRef ds:uri="94eab51b-fcae-4bce-a35e-bdc099b66db8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>